--- a/物资/采购清单.xlsx
+++ b/物资/采购清单.xlsx
@@ -2,17 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-13" sheetId="1" r:id="R6bdd18027fa049b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-21" sheetId="2" r:id="R3137b6066dfc44ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-22" sheetId="3" r:id="R5f1e6717845d46d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总计" sheetId="4" r:id="R595b446844a9483e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-24" sheetId="5" r:id="Rfc255b41d4de4531"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-28" sheetId="6" r:id="Rc74e662b14a3422b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-29" sheetId="7" r:id="Re13cb68caae14a33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-03" sheetId="8" r:id="R50def68157a14b31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-07" sheetId="9" r:id="Rd8906bde8b1e44f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-10" sheetId="10" r:id="Rb31dc7e28a3041ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-14" sheetId="11" r:id="R7af2020762274e74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-13" sheetId="1" r:id="R7b3b1a3bf4a14ec1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-21" sheetId="2" r:id="R77cc90ac011e4bd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-22" sheetId="3" r:id="R79b66a88c52342e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总计" sheetId="4" r:id="R53d87fa721b84c23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-24" sheetId="5" r:id="Rb675d243c7814053"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-28" sheetId="6" r:id="R18e5f622bccb4cf5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-29" sheetId="7" r:id="R9f9bb3f749fa4ff3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-03" sheetId="8" r:id="R09003a0ce9774da9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-07" sheetId="9" r:id="R181f63b7c8754bd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-10" sheetId="10" r:id="Rbd17915a09d74c7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-14" sheetId="11" r:id="R93708f1c8d754161"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-17" sheetId="12" r:id="Rbfdab296857a4f3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-18" sheetId="13" r:id="R7662135d211f406d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -30,7 +32,7 @@
     <x:numFmt numFmtId="203" formatCode="0.00"/>
     <x:numFmt numFmtId="204" formatCode="@"/>
   </x:numFmts>
-  <x:fonts count="24">
+  <x:fonts count="28">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -161,8 +163,30 @@
       <x:color rgb="FF1F1F1F"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF203040"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF203040"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF203040"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF203040"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="55">
+  <x:fills count="69">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -434,8 +458,78 @@
         <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF244062"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF5B9BD5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF244062"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF5B9BD5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="8">
+  <x:borders count="14">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -535,11 +629,71 @@
         <x:color rgb="FF1F4E78"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF5B9BD5"/>
+      </x:left>
+      <x:top style="medium">
+        <x:color rgb="FF1F4E78"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF5B9BD5"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="medium">
+        <x:color rgb="FF1F4E78"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF5B9BD5"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF5B9BD5"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF1F4E78"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF5B9BD5"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF5B9BD5"/>
+      </x:left>
+      <x:top style="medium">
+        <x:color rgb="FF1F4E78"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF1F4E78"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="medium">
+        <x:color rgb="FF1F4E78"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF1F4E78"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF5B9BD5"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF1F4E78"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF1F4E78"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="485">
+  <x:cellXfs count="686">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1742,6 +1896,493 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="21" fillId="54" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="55" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="55" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="55" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="55" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="56" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="56" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="56" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="56" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="57" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="57" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="57" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="57" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="57" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="57" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="58" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="58" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="58" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="58" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="58" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="56" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="56" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="56" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="56" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="56" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="56" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="56" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="58" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="58" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="56" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="58" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="56" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="56" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="25" fillId="58" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="16" fillId="56" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="21" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="21" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="21" fillId="58" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="21" fillId="58" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="21" fillId="58" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="58" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="26" fillId="58" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="26" fillId="58" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="26" fillId="58" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="58" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="26" fillId="58" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="26" fillId="58" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="26" fillId="58" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="58" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="59" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="59" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="59" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="16" fillId="59" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="59" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="59" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="16" fillId="59" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="59" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="59" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="59" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="59" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="59" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="59" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="59" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="59" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="59" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="60" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="60" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="16" fillId="60" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="60" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="60" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="60" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="60" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="24" fillId="60" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="60" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="60" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="60" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="24" fillId="60" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="60" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="60" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="24" fillId="60" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="60" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="60" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="61" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="61" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="61" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="61" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="61" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="61" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="61" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="61" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="61" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="61" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="61" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="16" fillId="61" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="62" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="62" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="62" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="62" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="64" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="64" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="64" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="64" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="64" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="64" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="65" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="65" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="65" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="65" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="65" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="65" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="65" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="65" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="25" fillId="65" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="63" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="63" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="63" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="63" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="63" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="63" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="63" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="63" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="63" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="63" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="63" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="16" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="16" fillId="65" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="65" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="65" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="65" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="24" fillId="65" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="65" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="24" fillId="65" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="65" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="24" fillId="65" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="65" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="24" fillId="65" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="65" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="66" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="66" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="66" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="16" fillId="66" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="66" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="66" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="16" fillId="66" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="66" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="66" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="66" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="66" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="66" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="66" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="66" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="66" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="66" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="67" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="67" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="67" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="67" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="67" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="67" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="67" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="67" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="27" fillId="67" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="67" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="67" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="67" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="67" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="27" fillId="67" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="67" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="67" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="67" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="27" fillId="67" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="67" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="67" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="67" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="67" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="68" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="68" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="68" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="68" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="68" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="68" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="68" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="68" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="68" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="68" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="68" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="68" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -2689,6 +3330,568 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="27" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="488" t="str">
+        <x:v>2026-08-17 采购清单</x:v>
+      </x:c>
+      <x:c r="B1" s="488"/>
+      <x:c r="C1" s="488"/>
+      <x:c r="D1" s="488"/>
+      <x:c r="E1" s="488"/>
+      <x:c r="F1" s="488"/>
+      <x:c r="G1" s="488"/>
+      <x:c r="H1" s="488"/>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="492" t="str">
+        <x:v>采购日期：2026-08-17</x:v>
+      </x:c>
+      <x:c r="B2" s="492"/>
+      <x:c r="C2" s="492"/>
+      <x:c r="D2" s="492"/>
+      <x:c r="E2" s="492"/>
+      <x:c r="F2" s="492"/>
+      <x:c r="G2" s="492"/>
+      <x:c r="H2" s="492"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="498" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B3" s="498" t="str">
+        <x:v>商品名称</x:v>
+      </x:c>
+      <x:c r="C3" s="498" t="str">
+        <x:v>规格/型号</x:v>
+      </x:c>
+      <x:c r="D3" s="498" t="str">
+        <x:v>数量</x:v>
+      </x:c>
+      <x:c r="E3" s="498" t="str">
+        <x:v>单价（元）</x:v>
+      </x:c>
+      <x:c r="F3" s="498" t="str">
+        <x:v>金额（元）</x:v>
+      </x:c>
+      <x:c r="G3" s="498" t="str">
+        <x:v>店铺</x:v>
+      </x:c>
+      <x:c r="H3" s="498" t="str">
+        <x:v>备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="42" customHeight="1">
+      <x:c r="A4" s="511" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="512" t="str">
+        <x:v>美标特软硅胶线</x:v>
+      </x:c>
+      <x:c r="C4" s="512" t="str">
+        <x:v>28AWG / 黑色 / 10米/卷</x:v>
+      </x:c>
+      <x:c r="D4" s="511" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="517" t="n">
+        <x:v>8.49</x:v>
+      </x:c>
+      <x:c r="F4" s="517" t="n">
+        <x:f>D4*E4</x:f>
+        <x:v>8.49</x:v>
+      </x:c>
+      <x:c r="G4" s="512" t="str">
+        <x:v>skygod旗舰店</x:v>
+      </x:c>
+      <x:c r="H4" s="512" t="str">
+        <x:v>优惠后价；先用后付</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="511" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B5" s="512" t="str">
+        <x:v>美标特软硅胶线</x:v>
+      </x:c>
+      <x:c r="C5" s="512" t="str">
+        <x:v>28AWG / 红色 / 10米/卷</x:v>
+      </x:c>
+      <x:c r="D5" s="511" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="517" t="n">
+        <x:v>8.49</x:v>
+      </x:c>
+      <x:c r="F5" s="517" t="n">
+        <x:f>D5*E5</x:f>
+        <x:v>8.49</x:v>
+      </x:c>
+      <x:c r="G5" s="512" t="str">
+        <x:v>skygod旗舰店</x:v>
+      </x:c>
+      <x:c r="H5" s="512" t="str">
+        <x:v>优惠后价；先用后付</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="511" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B6" s="512" t="str">
+        <x:v>XT60母对母延长线</x:v>
+      </x:c>
+      <x:c r="C6" s="512" t="str">
+        <x:v>0.2m / XT60母对母 / 10AWG（5.3mm²）</x:v>
+      </x:c>
+      <x:c r="D6" s="511" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" s="517" t="n">
+        <x:v>15.88</x:v>
+      </x:c>
+      <x:c r="F6" s="517" t="n">
+        <x:f>D6*E6</x:f>
+        <x:v>15.88</x:v>
+      </x:c>
+      <x:c r="G6" s="512" t="str">
+        <x:v>安捷达线束</x:v>
+      </x:c>
+      <x:c r="H6" s="512" t="str">
+        <x:v>免密支付；包邮</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="511" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B7" s="512" t="str">
+        <x:v>六角铜柱机箱螺丝钉</x:v>
+      </x:c>
+      <x:c r="C7" s="512" t="str">
+        <x:v>M3×20+6 / 20颗</x:v>
+      </x:c>
+      <x:c r="D7" s="511" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" s="517" t="n">
+        <x:v>5.66</x:v>
+      </x:c>
+      <x:c r="F7" s="517" t="n">
+        <x:f>D7*E7</x:f>
+        <x:v>5.66</x:v>
+      </x:c>
+      <x:c r="G7" s="512" t="str">
+        <x:v>固万基官方旗舰店</x:v>
+      </x:c>
+      <x:c r="H7" s="512" t="str">
+        <x:v>优惠后价；先用后付</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="54" customHeight="1">
+      <x:c r="A8" s="563" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="566" t="str">
+        <x:v>304不锈钢杯头内六角螺钉</x:v>
+      </x:c>
+      <x:c r="C8" s="566" t="str">
+        <x:v>M3×16 / 100个</x:v>
+      </x:c>
+      <x:c r="D8" s="563" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="564" t="n">
+        <x:v>3.63</x:v>
+      </x:c>
+      <x:c r="F8" s="564" t="n">
+        <x:f>D8*E8</x:f>
+        <x:v>3.63</x:v>
+      </x:c>
+      <x:c r="G8" s="566" t="str">
+        <x:v>楚卫旗舰店</x:v>
+      </x:c>
+      <x:c r="H8" s="566" t="str">
+        <x:v>先用后付；当前实付0元，预计自动扣款3.63元；订单号3316977480159071850</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="26" customHeight="1">
+      <x:c r="A9" s="575" t="str">
+        <x:v>本日合计</x:v>
+      </x:c>
+      <x:c r="B9" s="576"/>
+      <x:c r="C9" s="576"/>
+      <x:c r="D9" s="576" t="n">
+        <x:f>SUM(D4:D8)</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E9" s="578"/>
+      <x:c r="F9" s="578" t="n">
+        <x:f>SUM(F4:F8)</x:f>
+        <x:v>42.15</x:v>
+      </x:c>
+      <x:c r="G9" s="573"/>
+      <x:c r="H9" s="574"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A9:C9"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="31" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="582" t="str">
+        <x:v>2026-08-18 采购清单</x:v>
+      </x:c>
+      <x:c r="B1" s="582"/>
+      <x:c r="C1" s="582"/>
+      <x:c r="D1" s="582"/>
+      <x:c r="E1" s="582"/>
+      <x:c r="F1" s="582"/>
+      <x:c r="G1" s="582"/>
+      <x:c r="H1" s="582"/>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="586" t="str">
+        <x:v>采购日期：2026-08-18</x:v>
+      </x:c>
+      <x:c r="B2" s="586"/>
+      <x:c r="C2" s="586"/>
+      <x:c r="D2" s="586"/>
+      <x:c r="E2" s="586"/>
+      <x:c r="F2" s="586"/>
+      <x:c r="G2" s="586"/>
+      <x:c r="H2" s="586"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="592" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B3" s="592" t="str">
+        <x:v>商品名称</x:v>
+      </x:c>
+      <x:c r="C3" s="592" t="str">
+        <x:v>规格/型号</x:v>
+      </x:c>
+      <x:c r="D3" s="592" t="str">
+        <x:v>数量</x:v>
+      </x:c>
+      <x:c r="E3" s="592" t="str">
+        <x:v>单价（元）</x:v>
+      </x:c>
+      <x:c r="F3" s="592" t="str">
+        <x:v>金额（元）</x:v>
+      </x:c>
+      <x:c r="G3" s="592" t="str">
+        <x:v>店铺</x:v>
+      </x:c>
+      <x:c r="H3" s="592" t="str">
+        <x:v>备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="54" customHeight="1">
+      <x:c r="A4" s="598" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="599" t="str">
+        <x:v>M10密封舱实心螺栓</x:v>
+      </x:c>
+      <x:c r="C4" s="599" t="str">
+        <x:v>铝制密封螺丝 / M10</x:v>
+      </x:c>
+      <x:c r="D4" s="598" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E4" s="603" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F4" s="603" t="n">
+        <x:f>D4*E4</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G4" s="599" t="str">
+        <x:v>天启ROV97</x:v>
+      </x:c>
+      <x:c r="H4" s="599" t="str">
+        <x:v>包邮；与M10穿线螺丝同单合计370元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="54" customHeight="1">
+      <x:c r="A5" s="598" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B5" s="599" t="str">
+        <x:v>M10穿线螺丝</x:v>
+      </x:c>
+      <x:c r="C5" s="599" t="str">
+        <x:v>银色 / 不锈钢 / M10</x:v>
+      </x:c>
+      <x:c r="D5" s="598" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E5" s="603" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F5" s="603" t="n">
+        <x:f>D5*E5</x:f>
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="G5" s="599" t="str">
+        <x:v>天启ROV97</x:v>
+      </x:c>
+      <x:c r="H5" s="599" t="str">
+        <x:v>包邮；与密封舱实心螺栓同单合计370元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="54" customHeight="1">
+      <x:c r="A6" s="598" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B6" s="599" t="str">
+        <x:v>TS60水下推进器</x:v>
+      </x:c>
+      <x:c r="C6" s="599" t="str">
+        <x:v>蓝黑500KV正桨 / 推荐12V使用</x:v>
+      </x:c>
+      <x:c r="D6" s="598" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="603" t="n">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="F6" s="603" t="n">
+        <x:f>D6*E6</x:f>
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="G6" s="599" t="str">
+        <x:v>天启ROV97</x:v>
+      </x:c>
+      <x:c r="H6" s="599" t="str">
+        <x:v>包邮；与电调、密封舱同单；优惠后合计1997元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="54" customHeight="1">
+      <x:c r="A7" s="598" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B7" s="599" t="str">
+        <x:v>35A双向无刷电调</x:v>
+      </x:c>
+      <x:c r="C7" s="599" t="str">
+        <x:v>35A / 双向 / 水下动力</x:v>
+      </x:c>
+      <x:c r="D7" s="598" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="603" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F7" s="603" t="n">
+        <x:f>D7*E7</x:f>
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="G7" s="599" t="str">
+        <x:v>天启ROV97</x:v>
+      </x:c>
+      <x:c r="H7" s="599" t="str">
+        <x:v>包邮；与推进器、密封舱同单；优惠后合计1997元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="78" customHeight="1">
+      <x:c r="A8" s="598" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="599" t="str">
+        <x:v>海目云水下机器人密封舱</x:v>
+      </x:c>
+      <x:c r="C8" s="685" t="str">
+        <x:v>外径160mm×300mm / 亚克力圆管+半球罩+法兰+金属圈+端盖+密封圈+硅脂+配套螺丝</x:v>
+      </x:c>
+      <x:c r="D8" s="598" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="603" t="n">
+        <x:v>1145</x:v>
+      </x:c>
+      <x:c r="F8" s="603" t="n">
+        <x:f>D8*E8</x:f>
+        <x:v>1145</x:v>
+      </x:c>
+      <x:c r="G8" s="599" t="str">
+        <x:v>VIOCEAN海目云海洋科技企业店</x:v>
+      </x:c>
+      <x:c r="H8" s="685" t="str">
+        <x:v>优惠后价1145元（标价1150元）；整套含亚克力圆管、半球罩、法兰、金属圈、端盖、密封圈、硅脂和配套螺丝；与推进器、电调同单合计1997元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="54" customHeight="1">
+      <x:c r="A9" s="667" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B9" s="671" t="str">
+        <x:v>八合一大电流分电板</x:v>
+      </x:c>
+      <x:c r="C9" s="671" t="str">
+        <x:v>输入XT90 / 输出XT60 / 焊好出货</x:v>
+      </x:c>
+      <x:c r="D9" s="667" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E9" s="668" t="n">
+        <x:v>97.5</x:v>
+      </x:c>
+      <x:c r="F9" s="668" t="n">
+        <x:f>D9*E9</x:f>
+        <x:v>97.5</x:v>
+      </x:c>
+      <x:c r="G9" s="671" t="str">
+        <x:v>梁小二模型</x:v>
+      </x:c>
+      <x:c r="H9" s="671" t="str">
+        <x:v>商品97.50元；运费5.00元另列；实付款102.50元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="54" customHeight="1">
+      <x:c r="A10" s="667" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B10" s="671" t="str">
+        <x:v>XT90H黑色母头带线</x:v>
+      </x:c>
+      <x:c r="C10" s="671" t="str">
+        <x:v>XT90H黑母头 / 8AWG（8.29mm²）/ 红黑线 / 10cm</x:v>
+      </x:c>
+      <x:c r="D10" s="667" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E10" s="668" t="n">
+        <x:v>10.12</x:v>
+      </x:c>
+      <x:c r="F10" s="668" t="n">
+        <x:f>D10*E10</x:f>
+        <x:v>10.12</x:v>
+      </x:c>
+      <x:c r="G10" s="671" t="str">
+        <x:v>阳光模型上海DIY（截图店名截断）</x:v>
+      </x:c>
+      <x:c r="H10" s="671" t="str">
+        <x:v>先用后付；确认收货后应付10.12元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="54" customHeight="1">
+      <x:c r="A11" s="667" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B11" s="671" t="str">
+        <x:v>XT90H黄色公头带线</x:v>
+      </x:c>
+      <x:c r="C11" s="671" t="str">
+        <x:v>XT90H黄公头 / 8AWG（8.29mm²）/ 红黑线 / 10cm</x:v>
+      </x:c>
+      <x:c r="D11" s="667" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E11" s="668" t="n">
+        <x:v>11.11</x:v>
+      </x:c>
+      <x:c r="F11" s="668" t="n">
+        <x:f>D11*E11</x:f>
+        <x:v>11.11</x:v>
+      </x:c>
+      <x:c r="G11" s="671" t="str">
+        <x:v>阳光模型上海DIY（截图店名截断）</x:v>
+      </x:c>
+      <x:c r="H11" s="671" t="str">
+        <x:v>先用后付；确认收货后应付11.11元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="54" customHeight="1">
+      <x:c r="A12" s="667" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B12" s="671" t="str">
+        <x:v>运费</x:v>
+      </x:c>
+      <x:c r="C12" s="671" t="str">
+        <x:v>分电板订单运费</x:v>
+      </x:c>
+      <x:c r="D12" s="667" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" s="668" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F12" s="668" t="n">
+        <x:f>D12*E12</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G12" s="671" t="str">
+        <x:v>梁小二模型</x:v>
+      </x:c>
+      <x:c r="H12" s="671" t="str">
+        <x:v>分电板订单：实付款102.50元=商品97.50元+运费5.00元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="26" customHeight="1">
+      <x:c r="A13" s="681" t="str">
+        <x:v>本日合计</x:v>
+      </x:c>
+      <x:c r="B13" s="682"/>
+      <x:c r="C13" s="682"/>
+      <x:c r="D13" s="682" t="n">
+        <x:f>SUM(D4:D12)</x:f>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E13" s="684"/>
+      <x:c r="F13" s="684" t="n">
+        <x:f>SUM(F4:F12)</x:f>
+        <x:v>2490.73</x:v>
+      </x:c>
+      <x:c r="G13" s="679"/>
+      <x:c r="H13" s="680"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A13:C13"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -3733,23 +4936,63 @@
         <x:v>详见 2026-08-14 分表</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="30" customHeight="1">
-      <x:c r="A15" s="480" t="str">
+    <x:row r="15" ht="26" customHeight="1">
+      <x:c r="A15" s="530" t="n">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="B15" s="531" t="n">
+        <x:f>COUNTA('2026-08-17'!B4:B8)</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C15" s="531" t="n">
+        <x:f>'2026-08-17'!D9</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D15" s="532" t="n">
+        <x:f>'2026-08-17'!F9</x:f>
+        <x:v>42.15</x:v>
+      </x:c>
+      <x:c r="E15" s="533" t="str">
+        <x:v>详见 2026-08-17 分表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="26" customHeight="1">
+      <x:c r="A16" s="631" t="n">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="B16" s="632" t="n">
+        <x:f>COUNTA('2026-08-18'!B4:B12)</x:f>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C16" s="632" t="n">
+        <x:f>'2026-08-18'!D13</x:f>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D16" s="633" t="n">
+        <x:f>'2026-08-18'!F13</x:f>
+        <x:v>2490.73</x:v>
+      </x:c>
+      <x:c r="E16" s="634" t="str">
+        <x:v>详见 2026-08-18 分表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="26" customHeight="1">
+      <x:c r="A17" s="647" t="str">
         <x:v>总计</x:v>
       </x:c>
-      <x:c r="B15" s="483" t="n">
-        <x:f>SUM(B5:B14)</x:f>
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C15" s="483" t="n">
-        <x:f>SUM(C5:C14)</x:f>
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D15" s="484" t="n">
-        <x:f>SUM(D5:D14)</x:f>
-        <x:v>4202.8099999999995</x:v>
-      </x:c>
-      <x:c r="E15" s="482" t="str">
+      <x:c r="B17" s="648" t="n">
+        <x:f>SUM(B5:B16)</x:f>
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C17" s="648" t="n">
+        <x:f>SUM(C5:C16)</x:f>
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D17" s="649" t="n">
+        <x:f>SUM(D5:D16)</x:f>
+        <x:v>6735.689999999999</x:v>
+      </x:c>
+      <x:c r="E17" s="650" t="str">
         <x:v>全部采购记录</x:v>
       </x:c>
     </x:row>

--- a/物资/采购清单.xlsx
+++ b/物资/采购清单.xlsx
@@ -2,19 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-13" sheetId="1" r:id="R7b3b1a3bf4a14ec1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-21" sheetId="2" r:id="R77cc90ac011e4bd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-22" sheetId="3" r:id="R79b66a88c52342e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总计" sheetId="4" r:id="R53d87fa721b84c23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-24" sheetId="5" r:id="Rb675d243c7814053"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-28" sheetId="6" r:id="R18e5f622bccb4cf5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-29" sheetId="7" r:id="R9f9bb3f749fa4ff3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-03" sheetId="8" r:id="R09003a0ce9774da9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-07" sheetId="9" r:id="R181f63b7c8754bd9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-10" sheetId="10" r:id="Rbd17915a09d74c7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-14" sheetId="11" r:id="R93708f1c8d754161"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-17" sheetId="12" r:id="Rbfdab296857a4f3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-18" sheetId="13" r:id="R7662135d211f406d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-13" sheetId="1" r:id="Ra3100395eb3246ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-21" sheetId="2" r:id="R2639c71098c74b34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-22" sheetId="3" r:id="R9586f7f952c140b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总计" sheetId="4" r:id="R815ed4ae45ef457e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-24" sheetId="5" r:id="R8e15560767814379"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-28" sheetId="6" r:id="R38f2689dc5964806"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-29" sheetId="7" r:id="R9ead165662534684"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-03" sheetId="8" r:id="R9e0db58366524fb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-07" sheetId="9" r:id="R6e9593ea9d5b457d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-10" sheetId="10" r:id="R32e6e02225164bca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-14" sheetId="11" r:id="R9181c72511584dce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-17" sheetId="12" r:id="R9e6d0235243f4ef7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-18" sheetId="13" r:id="Ra1556f1e13444604"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-25" sheetId="14" r:id="Rfe9096cccaea4237"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-26" sheetId="15" r:id="R96336dfca3554b9c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -32,7 +34,7 @@
     <x:numFmt numFmtId="203" formatCode="0.00"/>
     <x:numFmt numFmtId="204" formatCode="@"/>
   </x:numFmts>
-  <x:fonts count="28">
+  <x:fonts count="29">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -185,8 +187,13 @@
       <x:color rgb="FF203040"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF203040"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="69">
+  <x:fills count="74">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -526,6 +533,31 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF244062"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF5B9BD5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -693,7 +725,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="686">
+  <x:cellXfs count="764">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2383,6 +2415,180 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="25" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="69" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="69" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="69" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="69" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="71" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="71" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="71" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="71" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="71" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="71" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="72" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="72" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="72" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="72" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="72" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="72" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="72" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="72" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="28" fillId="72" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="70" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="70" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="70" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="70" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="70" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="70" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="70" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="70" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="70" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="70" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="70" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="16" fillId="72" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="72" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="72" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="72" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="72" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="72" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="28" fillId="72" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="72" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="28" fillId="72" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="72" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="28" fillId="72" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="28" fillId="72" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="28" fillId="72" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="72" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="28" fillId="72" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="72" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="28" fillId="72" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="72" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="28" fillId="72" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="28" fillId="72" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="72" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="28" fillId="72" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="73" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="73" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="73" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="16" fillId="73" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="73" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="73" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="16" fillId="73" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="73" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="73" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="73" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="73" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="73" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="73" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="73" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="73" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="73" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -3892,6 +4098,460 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="31" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="689" t="str">
+        <x:v>2026-08-25 采购清单</x:v>
+      </x:c>
+      <x:c r="B1" s="689"/>
+      <x:c r="C1" s="689"/>
+      <x:c r="D1" s="689"/>
+      <x:c r="E1" s="689"/>
+      <x:c r="F1" s="689"/>
+      <x:c r="G1" s="689"/>
+      <x:c r="H1" s="689"/>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="693" t="str">
+        <x:v>采购日期：2026-08-25</x:v>
+      </x:c>
+      <x:c r="B2" s="693"/>
+      <x:c r="C2" s="693"/>
+      <x:c r="D2" s="693"/>
+      <x:c r="E2" s="693"/>
+      <x:c r="F2" s="693"/>
+      <x:c r="G2" s="693"/>
+      <x:c r="H2" s="693"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="699" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B3" s="699" t="str">
+        <x:v>商品名称</x:v>
+      </x:c>
+      <x:c r="C3" s="699" t="str">
+        <x:v>规格/型号</x:v>
+      </x:c>
+      <x:c r="D3" s="699" t="str">
+        <x:v>数量</x:v>
+      </x:c>
+      <x:c r="E3" s="699" t="str">
+        <x:v>单价（元）</x:v>
+      </x:c>
+      <x:c r="F3" s="699" t="str">
+        <x:v>金额（元）</x:v>
+      </x:c>
+      <x:c r="G3" s="699" t="str">
+        <x:v>店铺</x:v>
+      </x:c>
+      <x:c r="H3" s="699" t="str">
+        <x:v>备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="58" customHeight="1">
+      <x:c r="A4" s="705" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="706" t="str">
+        <x:v>密封舱气密性测试套装</x:v>
+      </x:c>
+      <x:c r="C4" s="706" t="str">
+        <x:v>真空枪+宝塔气嘴 / 工具箱套装</x:v>
+      </x:c>
+      <x:c r="D4" s="705" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="708" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="F4" s="708" t="n">
+        <x:f>D4*E4</x:f>
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="G4" s="706" t="str">
+        <x:v>VIOCEAN海目云海洋科技企业店</x:v>
+      </x:c>
+      <x:c r="H4" s="706" t="str">
+        <x:v>实付款245元；图1、2为同一订单，去重登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="58" customHeight="1">
+      <x:c r="A5" s="705" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B5" s="706" t="str">
+        <x:v>黑色快干AB环氧树脂胶</x:v>
+      </x:c>
+      <x:c r="C5" s="706" t="str">
+        <x:v>黑色快干款 / 5分钟初固 / 两支装 / 送工具</x:v>
+      </x:c>
+      <x:c r="D5" s="705" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="708" t="n">
+        <x:v>15.1</x:v>
+      </x:c>
+      <x:c r="F5" s="708" t="n">
+        <x:f>D5*E5</x:f>
+        <x:v>15.1</x:v>
+      </x:c>
+      <x:c r="G5" s="706" t="str">
+        <x:v>固万旗舰店</x:v>
+      </x:c>
+      <x:c r="H5" s="706" t="str">
+        <x:v>先用后付；确认收货后应付15.10元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="58" customHeight="1">
+      <x:c r="A6" s="705" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B6" s="706" t="str">
+        <x:v>4S6P水下机器人锂电池</x:v>
+      </x:c>
+      <x:c r="C6" s="706" t="str">
+        <x:v>14.8V / 18Ah / 4S6P</x:v>
+      </x:c>
+      <x:c r="D6" s="705" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" s="708" t="n">
+        <x:v>1552</x:v>
+      </x:c>
+      <x:c r="F6" s="708" t="n">
+        <x:f>D6*E6</x:f>
+        <x:v>1552</x:v>
+      </x:c>
+      <x:c r="G6" s="706" t="str">
+        <x:v>仙藤电池</x:v>
+      </x:c>
+      <x:c r="H6" s="706" t="str">
+        <x:v>实付款1552.00元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="26" customHeight="1">
+      <x:c r="A7" s="724" t="str">
+        <x:v>本日合计</x:v>
+      </x:c>
+      <x:c r="B7" s="721"/>
+      <x:c r="C7" s="721"/>
+      <x:c r="D7" s="721" t="n">
+        <x:f>SUM(D4:D6)</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="722"/>
+      <x:c r="F7" s="722" t="n">
+        <x:f>SUM(F4:F6)</x:f>
+        <x:v>1812.1</x:v>
+      </x:c>
+      <x:c r="G7" s="720"/>
+      <x:c r="H7" s="723"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A7:C7"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="31" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="689" t="str">
+        <x:v>2026-08-26 采购清单</x:v>
+      </x:c>
+      <x:c r="B1" s="689"/>
+      <x:c r="C1" s="689"/>
+      <x:c r="D1" s="689"/>
+      <x:c r="E1" s="689"/>
+      <x:c r="F1" s="689"/>
+      <x:c r="G1" s="689"/>
+      <x:c r="H1" s="689"/>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="693" t="str">
+        <x:v>采购日期：2026-08-26</x:v>
+      </x:c>
+      <x:c r="B2" s="693"/>
+      <x:c r="C2" s="693"/>
+      <x:c r="D2" s="693"/>
+      <x:c r="E2" s="693"/>
+      <x:c r="F2" s="693"/>
+      <x:c r="G2" s="693"/>
+      <x:c r="H2" s="693"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="699" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B3" s="699" t="str">
+        <x:v>商品名称</x:v>
+      </x:c>
+      <x:c r="C3" s="699" t="str">
+        <x:v>规格/型号</x:v>
+      </x:c>
+      <x:c r="D3" s="699" t="str">
+        <x:v>数量</x:v>
+      </x:c>
+      <x:c r="E3" s="699" t="str">
+        <x:v>单价（元）</x:v>
+      </x:c>
+      <x:c r="F3" s="699" t="str">
+        <x:v>金额（元）</x:v>
+      </x:c>
+      <x:c r="G3" s="699" t="str">
+        <x:v>店铺</x:v>
+      </x:c>
+      <x:c r="H3" s="699" t="str">
+        <x:v>备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="58" customHeight="1">
+      <x:c r="A4" s="705" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="706" t="str">
+        <x:v>M2.5 304不锈钢六角螺母</x:v>
+      </x:c>
+      <x:c r="C4" s="706" t="str">
+        <x:v>M2.5 / 100个</x:v>
+      </x:c>
+      <x:c r="D4" s="705" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="708" t="n">
+        <x:v>2.46</x:v>
+      </x:c>
+      <x:c r="F4" s="708" t="n">
+        <x:f>D4*E4</x:f>
+        <x:v>2.46</x:v>
+      </x:c>
+      <x:c r="G4" s="706" t="str">
+        <x:v>金超官方旗舰店</x:v>
+      </x:c>
+      <x:c r="H4" s="706" t="str">
+        <x:v>先用后付；确认收货后应付2.46元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="58" customHeight="1">
+      <x:c r="A5" s="705" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B5" s="706" t="str">
+        <x:v>M2.5尼龙平垫片</x:v>
+      </x:c>
+      <x:c r="C5" s="706" t="str">
+        <x:v>M2.5×5×1mm / 200个</x:v>
+      </x:c>
+      <x:c r="D5" s="705" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="708" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F5" s="708" t="n">
+        <x:f>D5*E5</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G5" s="706" t="str">
+        <x:v>品诺塑胶垫圈供应商</x:v>
+      </x:c>
+      <x:c r="H5" s="706" t="str">
+        <x:v>先用后付；确认收货后应付4.00元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="58" customHeight="1">
+      <x:c r="A6" s="705" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B6" s="706" t="str">
+        <x:v>M2.5×8 304不锈钢十字圆头机牙螺钉</x:v>
+      </x:c>
+      <x:c r="C6" s="706" t="str">
+        <x:v>M2.5×8 / 200个</x:v>
+      </x:c>
+      <x:c r="D6" s="705" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" s="708" t="n">
+        <x:v>5.71</x:v>
+      </x:c>
+      <x:c r="F6" s="708" t="n">
+        <x:f>D6*E6</x:f>
+        <x:v>5.71</x:v>
+      </x:c>
+      <x:c r="G6" s="706" t="str">
+        <x:v>伯瑞特官方旗舰店</x:v>
+      </x:c>
+      <x:c r="H6" s="706" t="str">
+        <x:v>先用后付；确认收货后应付5.71元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="58" customHeight="1">
+      <x:c r="A7" s="705" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B7" s="706" t="str">
+        <x:v>M2.5×6 304不锈钢十字圆头机牙螺钉</x:v>
+      </x:c>
+      <x:c r="C7" s="706" t="str">
+        <x:v>M2.5×6 / 200个</x:v>
+      </x:c>
+      <x:c r="D7" s="705" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" s="708" t="n">
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="F7" s="708" t="n">
+        <x:f>D7*E7</x:f>
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="G7" s="706" t="str">
+        <x:v>伯瑞特官方旗舰店</x:v>
+      </x:c>
+      <x:c r="H7" s="706" t="str">
+        <x:v>先用后付；确认收货后应付5.07元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="58" customHeight="1">
+      <x:c r="A8" s="705" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="706" t="str">
+        <x:v>M2.5×10 304不锈钢十字圆头机牙螺钉</x:v>
+      </x:c>
+      <x:c r="C8" s="706" t="str">
+        <x:v>M2.5×10 / 200个</x:v>
+      </x:c>
+      <x:c r="D8" s="705" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="708" t="n">
+        <x:v>6.19</x:v>
+      </x:c>
+      <x:c r="F8" s="708" t="n">
+        <x:f>D8*E8</x:f>
+        <x:v>6.19</x:v>
+      </x:c>
+      <x:c r="G8" s="706" t="str">
+        <x:v>伯瑞特官方旗舰店</x:v>
+      </x:c>
+      <x:c r="H8" s="706" t="str">
+        <x:v>先用后付；确认收货后应付6.19元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="58" customHeight="1">
+      <x:c r="A9" s="705" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B9" s="706" t="str">
+        <x:v>黑色自锁式尼龙扎带</x:v>
+      </x:c>
+      <x:c r="C9" s="706" t="str">
+        <x:v>4×150mm / 黑色 / 500根</x:v>
+      </x:c>
+      <x:c r="D9" s="705" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E9" s="708" t="n">
+        <x:v>17.39</x:v>
+      </x:c>
+      <x:c r="F9" s="708" t="n">
+        <x:f>D9*E9</x:f>
+        <x:v>17.39</x:v>
+      </x:c>
+      <x:c r="G9" s="706" t="str">
+        <x:v>伯瑞特官方旗舰店</x:v>
+      </x:c>
+      <x:c r="H9" s="706" t="str">
+        <x:v>先用后付；确认收货后应付17.39元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="58" customHeight="1">
+      <x:c r="A10" s="705" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B10" s="706" t="str">
+        <x:v>M3×20 304不锈钢杯头内六角螺钉</x:v>
+      </x:c>
+      <x:c r="C10" s="706" t="str">
+        <x:v>M3×20 / 50个</x:v>
+      </x:c>
+      <x:c r="D10" s="705" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E10" s="708" t="n">
+        <x:v>1.12</x:v>
+      </x:c>
+      <x:c r="F10" s="708" t="n">
+        <x:f>D10*E10</x:f>
+        <x:v>1.12</x:v>
+      </x:c>
+      <x:c r="G10" s="706" t="str">
+        <x:v>资鑫旗舰店</x:v>
+      </x:c>
+      <x:c r="H10" s="706" t="str">
+        <x:v>先用后付；确认收货后应付1.12元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="26" customHeight="1">
+      <x:c r="A11" s="724" t="str">
+        <x:v>本日合计</x:v>
+      </x:c>
+      <x:c r="B11" s="721"/>
+      <x:c r="C11" s="721"/>
+      <x:c r="D11" s="721" t="n">
+        <x:f>SUM(D4:D10)</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E11" s="722"/>
+      <x:c r="F11" s="722" t="n">
+        <x:f>SUM(F4:F10)</x:f>
+        <x:v>41.940000000000005</x:v>
+      </x:c>
+      <x:c r="G11" s="720"/>
+      <x:c r="H11" s="723"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A11:C11"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -4977,22 +5637,62 @@
       </x:c>
     </x:row>
     <x:row r="17" ht="26" customHeight="1">
-      <x:c r="A17" s="647" t="str">
+      <x:c r="A17" s="738" t="n">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="B17" s="739" t="n">
+        <x:f>COUNTA('2026-08-25'!B4:B6)</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C17" s="739" t="n">
+        <x:f>'2026-08-25'!D7</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D17" s="740" t="n">
+        <x:f>'2026-08-25'!F7</x:f>
+        <x:v>1812.1</x:v>
+      </x:c>
+      <x:c r="E17" s="741" t="str">
+        <x:v>详见 2026-08-25 分表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="26" customHeight="1">
+      <x:c r="A18" s="738" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="B18" s="739" t="n">
+        <x:f>COUNTA('2026-08-26'!B4:B10)</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C18" s="739" t="n">
+        <x:f>'2026-08-26'!D11</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D18" s="740" t="n">
+        <x:f>'2026-08-26'!F11</x:f>
+        <x:v>41.940000000000005</x:v>
+      </x:c>
+      <x:c r="E18" s="741" t="str">
+        <x:v>详见 2026-08-26 分表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="26" customHeight="1">
+      <x:c r="A19" s="760" t="str">
         <x:v>总计</x:v>
       </x:c>
-      <x:c r="B17" s="648" t="n">
-        <x:f>SUM(B5:B16)</x:f>
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C17" s="648" t="n">
-        <x:f>SUM(C5:C16)</x:f>
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D17" s="649" t="n">
-        <x:f>SUM(D5:D16)</x:f>
-        <x:v>6735.689999999999</x:v>
-      </x:c>
-      <x:c r="E17" s="650" t="str">
+      <x:c r="B19" s="761" t="n">
+        <x:f>SUM(B5:B18)</x:f>
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C19" s="761" t="n">
+        <x:f>SUM(C5:C18)</x:f>
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D19" s="762" t="n">
+        <x:f>SUM(D5:D18)</x:f>
+        <x:v>8589.73</x:v>
+      </x:c>
+      <x:c r="E19" s="763" t="str">
         <x:v>全部采购记录</x:v>
       </x:c>
     </x:row>

--- a/物资/采购清单.xlsx
+++ b/物资/采购清单.xlsx
@@ -2,21 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-13" sheetId="1" r:id="Ra3100395eb3246ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-21" sheetId="2" r:id="R2639c71098c74b34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-22" sheetId="3" r:id="R9586f7f952c140b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总计" sheetId="4" r:id="R815ed4ae45ef457e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-24" sheetId="5" r:id="R8e15560767814379"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-28" sheetId="6" r:id="R38f2689dc5964806"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-29" sheetId="7" r:id="R9ead165662534684"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-03" sheetId="8" r:id="R9e0db58366524fb5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-07" sheetId="9" r:id="R6e9593ea9d5b457d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-10" sheetId="10" r:id="R32e6e02225164bca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-14" sheetId="11" r:id="R9181c72511584dce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-17" sheetId="12" r:id="R9e6d0235243f4ef7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-18" sheetId="13" r:id="Ra1556f1e13444604"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-25" sheetId="14" r:id="Rfe9096cccaea4237"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-26" sheetId="15" r:id="R96336dfca3554b9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-13" sheetId="1" r:id="R1084e13719fb46d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-21" sheetId="2" r:id="R87f2616367464519"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-22" sheetId="3" r:id="R2beb8cb55ad64986"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总计" sheetId="4" r:id="R61cc8384b83e4138"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-24" sheetId="5" r:id="Ra3cccc528ad94395"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-28" sheetId="6" r:id="R7a3afd37be5e42a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-29" sheetId="7" r:id="R8d7f7bfaa16c4f00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-03" sheetId="8" r:id="R4a83fe2412764fa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-07" sheetId="9" r:id="Rddeb41cfde2b412d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-10" sheetId="10" r:id="Rb519b17b08104888"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-14" sheetId="11" r:id="R758cea5744c04a8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-17" sheetId="12" r:id="R85ee919e89ec4d51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-18" sheetId="13" r:id="R4caa91a8e72449e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-25" sheetId="14" r:id="Rf894ddf71deb45c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-26" sheetId="15" r:id="R644d57b9b91e47ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-28" sheetId="16" r:id="R64df2bb374ab45e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-30" sheetId="17" r:id="R81aaada94ca84d44"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -34,7 +36,7 @@
     <x:numFmt numFmtId="203" formatCode="0.00"/>
     <x:numFmt numFmtId="204" formatCode="@"/>
   </x:numFmts>
-  <x:fonts count="29">
+  <x:fonts count="30">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -192,8 +194,13 @@
       <x:color rgb="FF203040"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF203040"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="74">
+  <x:fills count="79">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -533,6 +540,31 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF244062"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF5B9BD5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -725,7 +757,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="764">
+  <x:cellXfs count="841">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2588,6 +2620,179 @@
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="16" fillId="73" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="74" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="74" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="74" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="74" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="75" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="75" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="75" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="75" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="76" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="76" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="76" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="76" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="76" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="76" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="77" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="77" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="77" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="77" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="77" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="77" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="77" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="77" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="29" fillId="77" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="75" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="75" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="75" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="75" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="75" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="75" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="75" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="75" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="75" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="75" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="75" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="75" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="75" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="75" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="75" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="75" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="16" fillId="77" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="77" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="77" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="77" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="77" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="77" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="29" fillId="77" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="77" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="29" fillId="77" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="77" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="29" fillId="77" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="29" fillId="77" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="29" fillId="77" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="77" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="29" fillId="77" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="77" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="29" fillId="77" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="77" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="29" fillId="77" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="29" fillId="77" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="77" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="29" fillId="77" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="78" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="78" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="78" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="16" fillId="78" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="78" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="78" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="16" fillId="78" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="78" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="78" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="78" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="78" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="78" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="78" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="78" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="78" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="78" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -4552,6 +4757,433 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="34" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="767" t="str">
+        <x:v>2026-08-28 采购清单</x:v>
+      </x:c>
+      <x:c r="B1" s="767"/>
+      <x:c r="C1" s="767"/>
+      <x:c r="D1" s="767"/>
+      <x:c r="E1" s="767"/>
+      <x:c r="F1" s="767"/>
+      <x:c r="G1" s="767"/>
+      <x:c r="H1" s="767"/>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="771" t="str">
+        <x:v>采购日期：2026-08-28</x:v>
+      </x:c>
+      <x:c r="B2" s="771"/>
+      <x:c r="C2" s="771"/>
+      <x:c r="D2" s="771"/>
+      <x:c r="E2" s="771"/>
+      <x:c r="F2" s="771"/>
+      <x:c r="G2" s="771"/>
+      <x:c r="H2" s="771"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="777" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B3" s="777" t="str">
+        <x:v>商品名称</x:v>
+      </x:c>
+      <x:c r="C3" s="777" t="str">
+        <x:v>规格/型号</x:v>
+      </x:c>
+      <x:c r="D3" s="777" t="str">
+        <x:v>数量</x:v>
+      </x:c>
+      <x:c r="E3" s="777" t="str">
+        <x:v>单价（元）</x:v>
+      </x:c>
+      <x:c r="F3" s="777" t="str">
+        <x:v>金额（元）</x:v>
+      </x:c>
+      <x:c r="G3" s="777" t="str">
+        <x:v>店铺</x:v>
+      </x:c>
+      <x:c r="H3" s="777" t="str">
+        <x:v>备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="58" customHeight="1">
+      <x:c r="A4" s="783" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="784" t="str">
+        <x:v>ROV专用防水密封硅脂</x:v>
+      </x:c>
+      <x:c r="C4" s="784" t="str">
+        <x:v>水下密封专用硅脂</x:v>
+      </x:c>
+      <x:c r="D4" s="783" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="786" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F4" s="786" t="n">
+        <x:f>D4*E4</x:f>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G4" s="784" t="str">
+        <x:v>VIOCEAN海目云海洋科技企业店</x:v>
+      </x:c>
+      <x:c r="H4" s="784" t="str">
+        <x:v>已签收；商品金额49.00元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="58" customHeight="1">
+      <x:c r="A5" s="783" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B5" s="784" t="str">
+        <x:v>水下机器人穿线密封胶</x:v>
+      </x:c>
+      <x:c r="C5" s="784" t="str">
+        <x:v>400米耐压密封胶 / 赠推杆和5个胶管</x:v>
+      </x:c>
+      <x:c r="D5" s="783" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="786" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F5" s="786" t="n">
+        <x:f>D5*E5</x:f>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G5" s="784" t="str">
+        <x:v>VIOCEAN海目云海洋科技企业店</x:v>
+      </x:c>
+      <x:c r="H5" s="784" t="str">
+        <x:v>已签收；商品金额75.00元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="58" customHeight="1">
+      <x:c r="A6" s="783" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B6" s="784" t="str">
+        <x:v>ROV纯铅配重块</x:v>
+      </x:c>
+      <x:c r="C6" s="784" t="str">
+        <x:v>约200g/块</x:v>
+      </x:c>
+      <x:c r="D6" s="783" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E6" s="786" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F6" s="786" t="n">
+        <x:f>D6*E6</x:f>
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G6" s="784" t="str">
+        <x:v>VIOCEAN海目云海洋科技企业店</x:v>
+      </x:c>
+      <x:c r="H6" s="784" t="str">
+        <x:v>已签收；5块共115.00元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="58" customHeight="1">
+      <x:c r="A7" s="783" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B7" s="784" t="str">
+        <x:v>1:1 AB胶枪</x:v>
+      </x:c>
+      <x:c r="C7" s="784" t="str">
+        <x:v>AB胶枪 / 1比1</x:v>
+      </x:c>
+      <x:c r="D7" s="783" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" s="786" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F7" s="786" t="n">
+        <x:f>D7*E7</x:f>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G7" s="784" t="str">
+        <x:v>VIOCEAN海目云海洋科技企业店</x:v>
+      </x:c>
+      <x:c r="H7" s="784" t="str">
+        <x:v>已签收；商品金额45.00元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="58" customHeight="1">
+      <x:c r="A8" s="783" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="784" t="str">
+        <x:v>运费</x:v>
+      </x:c>
+      <x:c r="C8" s="784" t="str">
+        <x:v>VIOCEAN订单运费</x:v>
+      </x:c>
+      <x:c r="D8" s="783" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="786" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F8" s="786" t="n">
+        <x:f>D8*E8</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G8" s="784" t="str">
+        <x:v>VIOCEAN海目云海洋科技企业店</x:v>
+      </x:c>
+      <x:c r="H8" s="784" t="str">
+        <x:v>用户确认10.00元为运费；不计入资产原值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="58" customHeight="1">
+      <x:c r="A9" s="783" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B9" s="784" t="str">
+        <x:v>水下机器人ROV探照灯</x:v>
+      </x:c>
+      <x:c r="C9" s="784" t="str">
+        <x:v>6500K / ArduSub脉宽控制 / 100°光束角</x:v>
+      </x:c>
+      <x:c r="D9" s="783" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E9" s="786" t="n">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="F9" s="786" t="n">
+        <x:f>D9*E9</x:f>
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="G9" s="784" t="str">
+        <x:v>EXOCEAN拓洲智能</x:v>
+      </x:c>
+      <x:c r="H9" s="784" t="str">
+        <x:v>已签收；商品标价299.00元，订单实付311.00元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="58" customHeight="1">
+      <x:c r="A10" s="783" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B10" s="784" t="str">
+        <x:v>运费</x:v>
+      </x:c>
+      <x:c r="C10" s="784" t="str">
+        <x:v>EXOCEAN订单运费</x:v>
+      </x:c>
+      <x:c r="D10" s="783" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E10" s="786" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F10" s="786" t="n">
+        <x:f>D10*E10</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G10" s="784" t="str">
+        <x:v>EXOCEAN拓洲智能</x:v>
+      </x:c>
+      <x:c r="H10" s="784" t="str">
+        <x:v>用户确认12.00元为运费；不计入资产原值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="58" customHeight="1">
+      <x:c r="A11" s="783" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B11" s="784" t="str">
+        <x:v>M5×16 304不锈钢杯头内六角螺钉</x:v>
+      </x:c>
+      <x:c r="C11" s="784" t="str">
+        <x:v>M5×16 / 50个</x:v>
+      </x:c>
+      <x:c r="D11" s="783" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E11" s="786" t="n">
+        <x:v>5.36</x:v>
+      </x:c>
+      <x:c r="F11" s="786" t="n">
+        <x:f>D11*E11</x:f>
+        <x:v>5.36</x:v>
+      </x:c>
+      <x:c r="G11" s="784" t="str">
+        <x:v>伯瑞特官方旗舰店</x:v>
+      </x:c>
+      <x:c r="H11" s="784" t="str">
+        <x:v>先用后付；确认收货后应付5.36元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="26" customHeight="1">
+      <x:c r="A12" s="802" t="str">
+        <x:v>本日合计</x:v>
+      </x:c>
+      <x:c r="B12" s="799"/>
+      <x:c r="C12" s="799"/>
+      <x:c r="D12" s="799" t="n">
+        <x:f>SUM(D4:D11)</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E12" s="800"/>
+      <x:c r="F12" s="800" t="n">
+        <x:f>SUM(F4:F11)</x:f>
+        <x:v>610.36</x:v>
+      </x:c>
+      <x:c r="G12" s="798"/>
+      <x:c r="H12" s="801"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A12:C12"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="34" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="767" t="str">
+        <x:v>2026-08-30 采购清单</x:v>
+      </x:c>
+      <x:c r="B1" s="767"/>
+      <x:c r="C1" s="767"/>
+      <x:c r="D1" s="767"/>
+      <x:c r="E1" s="767"/>
+      <x:c r="F1" s="767"/>
+      <x:c r="G1" s="767"/>
+      <x:c r="H1" s="767"/>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="771" t="str">
+        <x:v>采购日期：2026-08-30</x:v>
+      </x:c>
+      <x:c r="B2" s="771"/>
+      <x:c r="C2" s="771"/>
+      <x:c r="D2" s="771"/>
+      <x:c r="E2" s="771"/>
+      <x:c r="F2" s="771"/>
+      <x:c r="G2" s="771"/>
+      <x:c r="H2" s="771"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="777" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B3" s="777" t="str">
+        <x:v>商品名称</x:v>
+      </x:c>
+      <x:c r="C3" s="777" t="str">
+        <x:v>规格/型号</x:v>
+      </x:c>
+      <x:c r="D3" s="777" t="str">
+        <x:v>数量</x:v>
+      </x:c>
+      <x:c r="E3" s="777" t="str">
+        <x:v>单价（元）</x:v>
+      </x:c>
+      <x:c r="F3" s="777" t="str">
+        <x:v>金额（元）</x:v>
+      </x:c>
+      <x:c r="G3" s="777" t="str">
+        <x:v>店铺</x:v>
+      </x:c>
+      <x:c r="H3" s="777" t="str">
+        <x:v>备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="58" customHeight="1">
+      <x:c r="A4" s="783" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="784" t="str">
+        <x:v>绿林高纯度焊锡丝</x:v>
+      </x:c>
+      <x:c r="C4" s="784" t="str">
+        <x:v>锡含量63% / 0.8mm / 50g / 自带松香</x:v>
+      </x:c>
+      <x:c r="D4" s="783" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E4" s="786" t="n">
+        <x:v>15.8</x:v>
+      </x:c>
+      <x:c r="F4" s="786" t="n">
+        <x:f>D4*E4</x:f>
+        <x:v>31.6</x:v>
+      </x:c>
+      <x:c r="G4" s="784" t="str">
+        <x:v>绿林官方旗舰店</x:v>
+      </x:c>
+      <x:c r="H4" s="784" t="str">
+        <x:v>先用后付；确认收货后应付31.60元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="26" customHeight="1">
+      <x:c r="A5" s="802" t="str">
+        <x:v>本日合计</x:v>
+      </x:c>
+      <x:c r="B5" s="799"/>
+      <x:c r="C5" s="799"/>
+      <x:c r="D5" s="799" t="n">
+        <x:f>SUM(D4:D4)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E5" s="800"/>
+      <x:c r="F5" s="800" t="n">
+        <x:f>SUM(F4:F4)</x:f>
+        <x:v>31.6</x:v>
+      </x:c>
+      <x:c r="G5" s="798"/>
+      <x:c r="H5" s="801"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A5:C5"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -5677,22 +6309,62 @@
       </x:c>
     </x:row>
     <x:row r="19" ht="26" customHeight="1">
-      <x:c r="A19" s="760" t="str">
+      <x:c r="A19" s="815" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="B19" s="816" t="n">
+        <x:f>COUNTA('2026-08-28'!B4:B11)</x:f>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C19" s="816" t="n">
+        <x:f>'2026-08-28'!D12</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D19" s="817" t="n">
+        <x:f>'2026-08-28'!F12</x:f>
+        <x:v>610.36</x:v>
+      </x:c>
+      <x:c r="E19" s="818" t="str">
+        <x:v>详见 2026-08-28 分表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="26" customHeight="1">
+      <x:c r="A20" s="815" t="n">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="B20" s="816" t="n">
+        <x:f>COUNTA('2026-08-30'!B4:B4)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C20" s="816" t="n">
+        <x:f>'2026-08-30'!D5</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D20" s="817" t="n">
+        <x:f>'2026-08-30'!F5</x:f>
+        <x:v>31.6</x:v>
+      </x:c>
+      <x:c r="E20" s="818" t="str">
+        <x:v>详见 2026-08-30 分表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="26" customHeight="1">
+      <x:c r="A21" s="837" t="str">
         <x:v>总计</x:v>
       </x:c>
-      <x:c r="B19" s="761" t="n">
-        <x:f>SUM(B5:B18)</x:f>
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C19" s="761" t="n">
-        <x:f>SUM(C5:C18)</x:f>
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D19" s="762" t="n">
-        <x:f>SUM(D5:D18)</x:f>
-        <x:v>8589.73</x:v>
-      </x:c>
-      <x:c r="E19" s="763" t="str">
+      <x:c r="B21" s="838" t="n">
+        <x:f>SUM(B5:B20)</x:f>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C21" s="838" t="n">
+        <x:f>SUM(C5:C20)</x:f>
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D21" s="839" t="n">
+        <x:f>SUM(D5:D20)</x:f>
+        <x:v>9231.69</x:v>
+      </x:c>
+      <x:c r="E21" s="840" t="str">
         <x:v>全部采购记录</x:v>
       </x:c>
     </x:row>

--- a/物资/采购清单.xlsx
+++ b/物资/采购清单.xlsx
@@ -2,23 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-13" sheetId="1" r:id="R1084e13719fb46d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-21" sheetId="2" r:id="R87f2616367464519"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-22" sheetId="3" r:id="R2beb8cb55ad64986"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总计" sheetId="4" r:id="R61cc8384b83e4138"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-24" sheetId="5" r:id="Ra3cccc528ad94395"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-28" sheetId="6" r:id="R7a3afd37be5e42a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-29" sheetId="7" r:id="R8d7f7bfaa16c4f00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-03" sheetId="8" r:id="R4a83fe2412764fa0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-07" sheetId="9" r:id="Rddeb41cfde2b412d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-10" sheetId="10" r:id="Rb519b17b08104888"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-14" sheetId="11" r:id="R758cea5744c04a8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-17" sheetId="12" r:id="R85ee919e89ec4d51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-18" sheetId="13" r:id="R4caa91a8e72449e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-25" sheetId="14" r:id="Rf894ddf71deb45c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-26" sheetId="15" r:id="R644d57b9b91e47ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-28" sheetId="16" r:id="R64df2bb374ab45e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-30" sheetId="17" r:id="R81aaada94ca84d44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-13" sheetId="1" r:id="R5b844ce3936747da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-21" sheetId="2" r:id="Rbe7b81884f4f4460"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-22" sheetId="3" r:id="R4e5cda2d0e4b40d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总计" sheetId="4" r:id="R7a95ed11156b4adc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-24" sheetId="5" r:id="R9b23dd99dacf48b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-28" sheetId="6" r:id="R7efbeaaba1444da6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07-29" sheetId="7" r:id="R3ac3abd60e8e440e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-03" sheetId="8" r:id="R047fa91f5c0d4f52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-07" sheetId="9" r:id="R94ddbfde15884e90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-10" sheetId="10" r:id="Rdbeac1613c7e4150"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-14" sheetId="11" r:id="R7529065cc1484f1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-17" sheetId="12" r:id="R243d8d4c9b294afd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-18" sheetId="13" r:id="Rb88b8da7d9304172"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-25" sheetId="14" r:id="Rd7e6447dc82943cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-26" sheetId="15" r:id="R9f3cb49e0f04425b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-28" sheetId="16" r:id="R5d0c7a0512484f33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-30" sheetId="17" r:id="R5d72227cf8b24b5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-02" sheetId="18" r:id="Ra78a2a867b874da8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-01" sheetId="19" r:id="Rfb61777808ef40a1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -29,14 +31,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="5">
+  <x:numFmts count="6">
     <x:numFmt numFmtId="200" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="201" formatCode="#,##0"/>
     <x:numFmt numFmtId="202" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="203" formatCode="0.00"/>
     <x:numFmt numFmtId="204" formatCode="@"/>
+    <x:numFmt numFmtId="205" formatCode="#,##0.000"/>
   </x:numFmts>
-  <x:fonts count="30">
+  <x:fonts count="32">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -199,8 +202,18 @@
       <x:color rgb="FF203040"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF203040"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF203040"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="79">
+  <x:fills count="89">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -540,6 +553,56 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF244062"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF5B9BD5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF244062"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF5B9BD5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -757,7 +820,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="841">
+  <x:cellXfs count="981">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2793,6 +2856,338 @@
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="16" fillId="78" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="79" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="79" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="79" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="79" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="80" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="80" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="80" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="80" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="81" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="81" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="81" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="81" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="81" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="81" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="82" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="30" fillId="82" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="30" fillId="82" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="30" fillId="82" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="82" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="82" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="82" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="82" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="30" fillId="82" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="80" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="80" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="80" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="80" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="80" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="80" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="80" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="80" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="80" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="80" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="80" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="80" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="80" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="80" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="80" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="80" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="16" fillId="82" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="82" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="82" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="82" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="30" fillId="82" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="82" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="30" fillId="82" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="82" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="30" fillId="82" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="82" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="30" fillId="82" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="82" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="83" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="83" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="83" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="16" fillId="83" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="83" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="83" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="16" fillId="83" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="83" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="83" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="83" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="83" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="83" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="83" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="83" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="83" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="83" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="84" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="84" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="84" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="84" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="85" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="85" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="85" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="85" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="86" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="86" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="86" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="86" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="86" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="86" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="87" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="87" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="87" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="87" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="87" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="87" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="87" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="87" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="31" fillId="87" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="31" fillId="87" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="85" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="85" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="85" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="85" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="85" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="85" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="85" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="85" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="85" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="85" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="85" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="85" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="85" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="85" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="85" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="85" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="25" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="25" fillId="87" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="87" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="25" fillId="87" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="87" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="31" fillId="87" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="87" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="31" fillId="87" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="87" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="16" fillId="87" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="87" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="87" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="87" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="31" fillId="87" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="87" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="31" fillId="87" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="87" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="88" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="88" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="88" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="16" fillId="88" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="88" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="88" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="16" fillId="88" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="88" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="88" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="88" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="88" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="88" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="88" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="88" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="88" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="88" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -5184,6 +5579,460 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="34" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="844" t="str">
+        <x:v>2026-09-02 采购清单</x:v>
+      </x:c>
+      <x:c r="B1" s="844"/>
+      <x:c r="C1" s="844"/>
+      <x:c r="D1" s="844"/>
+      <x:c r="E1" s="844"/>
+      <x:c r="F1" s="844"/>
+      <x:c r="G1" s="844"/>
+      <x:c r="H1" s="844"/>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="848" t="str">
+        <x:v>采购日期：2026-09-02</x:v>
+      </x:c>
+      <x:c r="B2" s="848"/>
+      <x:c r="C2" s="848"/>
+      <x:c r="D2" s="848"/>
+      <x:c r="E2" s="848"/>
+      <x:c r="F2" s="848"/>
+      <x:c r="G2" s="848"/>
+      <x:c r="H2" s="848"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="854" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B3" s="854" t="str">
+        <x:v>商品名称</x:v>
+      </x:c>
+      <x:c r="C3" s="854" t="str">
+        <x:v>规格/型号</x:v>
+      </x:c>
+      <x:c r="D3" s="854" t="str">
+        <x:v>数量</x:v>
+      </x:c>
+      <x:c r="E3" s="854" t="str">
+        <x:v>单价（元）</x:v>
+      </x:c>
+      <x:c r="F3" s="854" t="str">
+        <x:v>金额（元）</x:v>
+      </x:c>
+      <x:c r="G3" s="854" t="str">
+        <x:v>店铺</x:v>
+      </x:c>
+      <x:c r="H3" s="854" t="str">
+        <x:v>备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="58" customHeight="1">
+      <x:c r="A4" s="860" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="861" t="str">
+        <x:v>XT60并联转接头</x:v>
+      </x:c>
+      <x:c r="C4" s="861" t="str">
+        <x:v>XT60 两母一公</x:v>
+      </x:c>
+      <x:c r="D4" s="860" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="863" t="n">
+        <x:v>10.4</x:v>
+      </x:c>
+      <x:c r="F4" s="863" t="n">
+        <x:f>D4*E4</x:f>
+        <x:v>10.4</x:v>
+      </x:c>
+      <x:c r="G4" s="861" t="str">
+        <x:v>亿恒电子888</x:v>
+      </x:c>
+      <x:c r="H4" s="861" t="str">
+        <x:v>订单号33163934900009008294；已发货</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="58" customHeight="1">
+      <x:c r="A5" s="860" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B5" s="861" t="str">
+        <x:v>XT90公母头延长转接线</x:v>
+      </x:c>
+      <x:c r="C5" s="861" t="str">
+        <x:v>XT90公头转母头 / 10号线 / 30cm</x:v>
+      </x:c>
+      <x:c r="D5" s="860" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="863" t="n">
+        <x:v>15.7</x:v>
+      </x:c>
+      <x:c r="F5" s="863" t="n">
+        <x:f>D5*E5</x:f>
+        <x:v>15.7</x:v>
+      </x:c>
+      <x:c r="G5" s="861" t="str">
+        <x:v>亿恒电子888</x:v>
+      </x:c>
+      <x:c r="H5" s="861" t="str">
+        <x:v>订单号33163934900009008294；已发货</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="58" customHeight="1">
+      <x:c r="A6" s="860" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B6" s="861" t="str">
+        <x:v>4S平衡充电延长线（第1条）</x:v>
+      </x:c>
+      <x:c r="C6" s="861" t="str">
+        <x:v>4S（5线）/ 22AWG / 公转母 / 10cm</x:v>
+      </x:c>
+      <x:c r="D6" s="860" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" s="863" t="n">
+        <x:v>2.9</x:v>
+      </x:c>
+      <x:c r="F6" s="863" t="n">
+        <x:f>D6*E6</x:f>
+        <x:v>2.9</x:v>
+      </x:c>
+      <x:c r="G6" s="861" t="str">
+        <x:v>尼莱电子</x:v>
+      </x:c>
+      <x:c r="H6" s="861" t="str">
+        <x:v>订单号33163934900009053486；待发货</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="58" customHeight="1">
+      <x:c r="A7" s="860" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B7" s="861" t="str">
+        <x:v>4S平衡充电延长线（第2条）</x:v>
+      </x:c>
+      <x:c r="C7" s="861" t="str">
+        <x:v>4S（5线）/ 22AWG / 公转母 / 10cm</x:v>
+      </x:c>
+      <x:c r="D7" s="860" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" s="863" t="n">
+        <x:v>3.4</x:v>
+      </x:c>
+      <x:c r="F7" s="863" t="n">
+        <x:f>D7*E7</x:f>
+        <x:v>3.4</x:v>
+      </x:c>
+      <x:c r="G7" s="861" t="str">
+        <x:v>尼莱电子</x:v>
+      </x:c>
+      <x:c r="H7" s="861" t="str">
+        <x:v>截图所示规格文字相同，按订单第2条单列；待发货</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="58" customHeight="1">
+      <x:c r="A8" s="860" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="861" t="str">
+        <x:v>运费</x:v>
+      </x:c>
+      <x:c r="C8" s="861" t="str">
+        <x:v>尼莱电子订单运费</x:v>
+      </x:c>
+      <x:c r="D8" s="860" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="863" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F8" s="863" t="n">
+        <x:f>D8*E8</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G8" s="861" t="str">
+        <x:v>尼莱电子</x:v>
+      </x:c>
+      <x:c r="H8" s="861" t="str">
+        <x:v>商品合计6.30元+运费6.00元=实付12.30元；不计入资产原值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="58" customHeight="1">
+      <x:c r="A9" s="860" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B9" s="861" t="str">
+        <x:v>IMAX B6AC 80W平衡充电器</x:v>
+      </x:c>
+      <x:c r="C9" s="861" t="str">
+        <x:v>B6AC+XT90线 / 内置电源 / 80W</x:v>
+      </x:c>
+      <x:c r="D9" s="860" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E9" s="863" t="n">
+        <x:v>89.99</x:v>
+      </x:c>
+      <x:c r="F9" s="863" t="n">
+        <x:f>D9*E9</x:f>
+        <x:v>89.99</x:v>
+      </x:c>
+      <x:c r="G9" s="861" t="str">
+        <x:v>星星模型配件</x:v>
+      </x:c>
+      <x:c r="H9" s="861" t="str">
+        <x:v>订单号33163934900009099495；已发货</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="26" customHeight="1">
+      <x:c r="A10" s="879" t="str">
+        <x:v>本日合计</x:v>
+      </x:c>
+      <x:c r="B10" s="876"/>
+      <x:c r="C10" s="876"/>
+      <x:c r="D10" s="876" t="n">
+        <x:f>SUM(D4:D9)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E10" s="877"/>
+      <x:c r="F10" s="877" t="n">
+        <x:f>SUM(F4:F9)</x:f>
+        <x:v>128.39</x:v>
+      </x:c>
+      <x:c r="G10" s="875"/>
+      <x:c r="H10" s="878"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A10:C10"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="34" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="911" t="str">
+        <x:v>2026-09-01 采购清单</x:v>
+      </x:c>
+      <x:c r="B1" s="911"/>
+      <x:c r="C1" s="911"/>
+      <x:c r="D1" s="911"/>
+      <x:c r="E1" s="911"/>
+      <x:c r="F1" s="911"/>
+      <x:c r="G1" s="911"/>
+      <x:c r="H1" s="911"/>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="915" t="str">
+        <x:v>采购日期：2026-09-01</x:v>
+      </x:c>
+      <x:c r="B2" s="915"/>
+      <x:c r="C2" s="915"/>
+      <x:c r="D2" s="915"/>
+      <x:c r="E2" s="915"/>
+      <x:c r="F2" s="915"/>
+      <x:c r="G2" s="915"/>
+      <x:c r="H2" s="915"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="921" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B3" s="921" t="str">
+        <x:v>商品名称</x:v>
+      </x:c>
+      <x:c r="C3" s="921" t="str">
+        <x:v>规格/型号</x:v>
+      </x:c>
+      <x:c r="D3" s="921" t="str">
+        <x:v>数量</x:v>
+      </x:c>
+      <x:c r="E3" s="921" t="str">
+        <x:v>单价（元）</x:v>
+      </x:c>
+      <x:c r="F3" s="921" t="str">
+        <x:v>金额（元）</x:v>
+      </x:c>
+      <x:c r="G3" s="921" t="str">
+        <x:v>店铺</x:v>
+      </x:c>
+      <x:c r="H3" s="921" t="str">
+        <x:v>备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="58" customHeight="1">
+      <x:c r="A4" s="927" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="928" t="str">
+        <x:v>15件套充电式电动螺丝刀</x:v>
+      </x:c>
+      <x:c r="C4" s="928" t="str">
+        <x:v>15件套 / 充电式 / 手持电钻螺丝刀</x:v>
+      </x:c>
+      <x:c r="D4" s="927" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="930" t="n">
+        <x:v>27.84</x:v>
+      </x:c>
+      <x:c r="F4" s="930" t="n">
+        <x:f>D4*E4</x:f>
+        <x:v>27.84</x:v>
+      </x:c>
+      <x:c r="G4" s="928" t="str">
+        <x:v>鲸选坐标超市（西丽店）</x:v>
+      </x:c>
+      <x:c r="H4" s="928" t="str">
+        <x:v>订单已送达；截图实付27.84元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="58" customHeight="1">
+      <x:c r="A5" s="927" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B5" s="928" t="str">
+        <x:v>75%酒精消毒湿巾</x:v>
+      </x:c>
+      <x:c r="C5" s="928" t="str">
+        <x:v>带盖大包 / 75%酒精</x:v>
+      </x:c>
+      <x:c r="D5" s="927" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="930" t="n">
+        <x:v>5.97</x:v>
+      </x:c>
+      <x:c r="F5" s="930" t="n">
+        <x:f>D5*E5</x:f>
+        <x:v>5.97</x:v>
+      </x:c>
+      <x:c r="G5" s="928" t="str">
+        <x:v>鲸选坐标超市（西丽店）</x:v>
+      </x:c>
+      <x:c r="H5" s="928" t="str">
+        <x:v>订单已送达；截图实付5.97元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="58" customHeight="1">
+      <x:c r="A6" s="927" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B6" s="928" t="str">
+        <x:v>公牛PVC电工绝缘胶带</x:v>
+      </x:c>
+      <x:c r="C6" s="928" t="str">
+        <x:v>黑色 / 9米/卷 / 阻燃耐低温</x:v>
+      </x:c>
+      <x:c r="D6" s="927" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" s="930" t="n">
+        <x:v>3.02</x:v>
+      </x:c>
+      <x:c r="F6" s="930" t="n">
+        <x:f>D6*E6</x:f>
+        <x:v>3.02</x:v>
+      </x:c>
+      <x:c r="G6" s="928" t="str">
+        <x:v>鲸选坐标超市（西丽店）</x:v>
+      </x:c>
+      <x:c r="H6" s="928" t="str">
+        <x:v>订单已送达；截图实付3.02元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="58" customHeight="1">
+      <x:c r="A7" s="927" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B7" s="928" t="str">
+        <x:v>鹰牌水磨砂纸</x:v>
+      </x:c>
+      <x:c r="C7" s="928" t="str">
+        <x:v>150目</x:v>
+      </x:c>
+      <x:c r="D7" s="927" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E7" s="931" t="n">
+        <x:v>1.194</x:v>
+      </x:c>
+      <x:c r="F7" s="930" t="n">
+        <x:f>D7*E7</x:f>
+        <x:v>5.97</x:v>
+      </x:c>
+      <x:c r="G7" s="928" t="str">
+        <x:v>鲸选坐标超市（西丽店）</x:v>
+      </x:c>
+      <x:c r="H7" s="928" t="str">
+        <x:v>订单已送达；5张合计5.97元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="26" customHeight="1">
+      <x:c r="A8" s="947" t="str">
+        <x:v>本日合计</x:v>
+      </x:c>
+      <x:c r="B8" s="944"/>
+      <x:c r="C8" s="944"/>
+      <x:c r="D8" s="944" t="n">
+        <x:f>SUM(D4:D7)</x:f>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E8" s="945"/>
+      <x:c r="F8" s="945" t="n">
+        <x:f>SUM(F4:F7)</x:f>
+        <x:v>42.800000000000004</x:v>
+      </x:c>
+      <x:c r="G8" s="943"/>
+      <x:c r="H8" s="946"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A8:C8"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -6349,22 +7198,62 @@
       </x:c>
     </x:row>
     <x:row r="21" ht="26" customHeight="1">
-      <x:c r="A21" s="837" t="str">
+      <x:c r="A21" s="953" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="B21" s="954" t="n">
+        <x:f>COUNTA('2026-09-01'!B4:B7)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C21" s="954" t="n">
+        <x:f>'2026-09-01'!D8</x:f>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D21" s="955" t="n">
+        <x:f>'2026-09-01'!F8</x:f>
+        <x:v>42.800000000000004</x:v>
+      </x:c>
+      <x:c r="E21" s="956" t="str">
+        <x:v>详见 2026-09-01 分表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="26" customHeight="1">
+      <x:c r="A22" s="953" t="n">
+        <x:v>46267</x:v>
+      </x:c>
+      <x:c r="B22" s="954" t="n">
+        <x:f>COUNTA('2026-09-02'!B4:B9)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C22" s="954" t="n">
+        <x:f>'2026-09-02'!D10</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D22" s="955" t="n">
+        <x:f>'2026-09-02'!F10</x:f>
+        <x:v>128.39</x:v>
+      </x:c>
+      <x:c r="E22" s="956" t="str">
+        <x:v>详见 2026-09-02 分表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="26" customHeight="1">
+      <x:c r="A23" s="977" t="str">
         <x:v>总计</x:v>
       </x:c>
-      <x:c r="B21" s="838" t="n">
-        <x:f>SUM(B5:B20)</x:f>
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C21" s="838" t="n">
-        <x:f>SUM(C5:C20)</x:f>
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="D21" s="839" t="n">
-        <x:f>SUM(D5:D20)</x:f>
-        <x:v>9231.69</x:v>
-      </x:c>
-      <x:c r="E21" s="840" t="str">
+      <x:c r="B23" s="978" t="n">
+        <x:f>SUM(B5:B22)</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C23" s="978" t="n">
+        <x:f>SUM(C5:C22)</x:f>
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D23" s="979" t="n">
+        <x:f>SUM(D5:D22)</x:f>
+        <x:v>9402.88</x:v>
+      </x:c>
+      <x:c r="E23" s="980" t="str">
         <x:v>全部采购记录</x:v>
       </x:c>
     </x:row>
